--- a/data_extactor/batch_10_fa/trimmed/batch_0056_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0056_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی</t>
+          <t>نظارت | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید دور | بیان شفاهی | درک شفاهی | توجه انتخابی | استقامت بدنی | قدرت عضلات تنه</t>
+          <t>حساسیت به مسئله | بینایی دور | بیان شفاهی | درک شفاهی | توجه انتخابی | استقامت | قدرت تنه</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و سرگرمی | مربیان ورزشی | تکنسین‌های فوریت‌های پزشکی (EMT) | آتش‌نشانان | سرپرستان رده‌اول کارکنان خدمات فردی | پیراپزشکان فوریت‌های پزشکی | کارکنان امور تفریحی و اوقات فراغت</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | مربیان و متخصصان سلامت و توان‌بخشی ورزشی | تکنسین‌های فوریت‌های پزشکی | آتش‌نشانان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | استدلال استقرایی | دید نزدیک</t>
+          <t>حساسیت به مسئله | توجه انتخابی | استدلال قیاسی | بیان شفاهی | درک شفاهی | استدلال استقرایی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارشناسان عملیات فرودگاهی | افسران گمرک و حفاظت مرزی | سرپرستان رده‌اول نیروهای حراست و نگهبانی | ماموران نظارت و کنترل پارک خودرو | نگهبانان و ماموران حراست | کارشناسان مدیریت امور حفاظتی و امنیتی | پلیس مترو و راه‌آهن</t>
+          <t>کارشناسان عملیات فرودگاهی | ماموران گمرک و حفاظت مرزی | سرپرستان رده‌اول کارکنان حراست و انتظامات | ماموران کنترل و اعمال قانون پارک دوبله و توقف | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | روان‌شناسی | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس مدارس | ماموران هدایت ترافیک و نگهبانان تقاطع | آموزگاران دوره ابتدایی (به‌جز آموزش استثنایی) | مهمانداران و متصدیان خدمات مسافری | معلمان دوره ابتدایی آموزش استثنایی | دستیاران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | دستیاران آموزشی مدارس استثنایی</t>
+          <t>رانندگان سرویس مدارس | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مهمانداران و متصدیان خدمات مسافران | معلمان آموزش استثنایی دوره ابتدایی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | امور حقوقی و دولتی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مخابرات و ارتباطات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | قانون و دولت | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | مخابرات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نگهبانان و ماموران حراست | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | ماموران نظارت و کنترل پارک خودرو | افسران گشت پلیس و ماموران انتظامی | سرپرستان رده‌اول نیروهای حراست و نگهبانی</t>
+          <t>نگهبانان و ماموران حراست | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | سرپرستان رده‌اول کارکنان حراست و انتظامات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | امور حقوقی و دولتی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول نیروهای حراست و نگهبانی | کارشناسان بررسی، بازرسی و تحلیل تقلب | ماموران نظارت تصویری و بازرسان مراکز سرگرمی | مدیران پیشگیری از افت و خسارت کالا | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست</t>
+          <t>کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | ریاضیات</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فرآوری | خدمات مشتریان و خدمات فردی | پرسنلی و منابع انسانی | مدیریت و امور اداری | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | خدمات مشتری و شخصی | پرسنل و منابع انسانی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی | دید نزدیک | خلاقیت و ابتکار</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | قصابان و خردکنندگان گوشت | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | تولید مواد غذایی | تولید و فرآوری | آموزش و تدریس | پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | تولید و فرآوری | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | درک کتبی | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | وضوح گفتار | درک کتبی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرآشپزان و آشپزان ارشد | کارگران سالن پذیرایی، سلف‌سرویس و کمک‌متصدیان بار | کارکنان فست‌فود و پیشخوان رستوران‌ها | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران</t>
+          <t>سرآشپزان و آشپزان ارشد | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | کارگران پیشخوان و فست‌فود | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ترابری و حمل‌ونقل | ارتباطات و رسانه‌ها | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
+          <t>مدیریت و اداره | حمل و نقل | ارتباطات و رسانه | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | مرتب‌سازی اطلاعات | تشخیص گفتار</t>
+          <t>درک شفاهی | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | سرآشپزان و آشپزان ارشد | آشپزان رستوران‌ها | آشپزان غذاهای فوری | کارکنان فست‌فود و پیشخوان رستوران‌ها | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران</t>
+          <t>نانوایان و شیرینی‌پزان | سرآشپزان و آشپزان ارشد | آشپزان رستوران | آشپزان غذاهای فوری | کارگران پیشخوان و فست‌فود | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | تولید مواد غذایی | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | تولید و فرآوری</t>
+          <t>زبان انگلیسی | تولید مواد غذایی | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | درک شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | قصابان و خردکنندگان گوشت | سرآشپزان و آشپزان ارشد | آشپزان رستوران‌ها | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران</t>
+          <t>نانوایان و شیرینی‌پزان | قصابان و برش‌کاران گوشت | سرآشپزان و آشپزان ارشد | آشپزان رستوران | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید مواد غذایی | فروش و بازاریابی | مدیریت و امور اداری | تولید و فرآوری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید مواد غذایی | فروش و بازاریابی | مدیریت و اداره | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | روانی بیان ایده‌ها | حساسیت به مسئله | چابکی انگشتان | چابکی دستی | مرتب‌سازی اطلاعات | خلاقیت و ابتکار</t>
+          <t>بینایی نزدیک | روانی ایده‌ها | حساسیت به مسئله | مهارت انگشتان | مهارت دستی | ترتیب‌دهی اطلاعات | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نانوایان و شیرینی‌پزان | سرآشپزان و آشپزان ارشد | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران‌ها | کارگران آماده‌سازی و خردکردن مواد اولیه غذا | مدیران خدمات غذا و رستوران | سالن‌کاران و گارسون‌ها</t>
+          <t>نانوایان و شیرینی‌پزان | سرآشپزان و آشپزان ارشد | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | آشپزان رستوران | کارگران آماده‌سازی غذا | مدیران خدمات پذیرایی و غذا و نوشیدنی | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
